--- a/cds_files/KansasState_CDS_2022-2023.xlsx
+++ b/cds_files/KansasState_CDS_2022-2023.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="4">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="C4" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="5">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="C5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
